--- a/data/products/p-gsb-001/work/Clear-Budget.xlsx
+++ b/data/products/p-gsb-001/work/Clear-Budget.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="171">
   <si>
     <t xml:space="preserve">Clear Budget</t>
   </si>
@@ -393,6 +393,9 @@
   </si>
   <si>
     <t xml:space="preserve">Card payment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concert tickets</t>
   </si>
   <si>
     <t xml:space="preserve">Shoes</t>
@@ -1305,7 +1308,7 @@
                 <c:formatCode>\$#,##0.00;[RED]"-$"#,##0.00;\$0.00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>1992.09</c:v>
+                  <c:v>2112.09</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1313,11 +1316,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="17068865"/>
-        <c:axId val="64864604"/>
+        <c:axId val="88460589"/>
+        <c:axId val="3627449"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="17068865"/>
+        <c:axId val="88460589"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1349,7 +1352,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64864604"/>
+        <c:crossAx val="3627449"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1357,7 +1360,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="64864604"/>
+        <c:axId val="3627449"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1399,7 +1402,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17068865"/>
+        <c:crossAx val="88460589"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1716,7 +1719,7 @@
                   <c:v>1523.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>118.49</c:v>
+                  <c:v>238.49</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>200</c:v>
@@ -2403,11 +2406,11 @@
         <v>42</v>
       </c>
       <c r="D19" s="12" t="str">
-        <f aca="false">IF(SUMPRODUCT(COUNTIF(January!$C$7:$C$86,{"Rent","Weekly shop","Bus pass","Pizza night","Weekly shop","Phone bill","To emergency fund","Streaming","Card payment","Shoes"}))=0,"Done","To do")</f>
+        <f aca="false">IF(SUMPRODUCT(COUNTIF(January!$C$7:$C$86,{"Rent","Weekly shop","Bus pass","Pizza night","Weekly shop","Phone bill","To emergency fund","Streaming","Card payment","Concert tickets","Shoes"}))=0,"Done","To do")</f>
         <v>To do</v>
       </c>
       <c r="E19" s="13" t="str">
-        <f aca="false">IF(SUMPRODUCT(COUNTIF(January!$C$7:$C$86,{"Rent","Weekly shop","Bus pass","Pizza night","Weekly shop","Phone bill","To emergency fund","Streaming","Card payment","Shoes"}))=0,"","Clear the example in January (step 2)")</f>
+        <f aca="false">IF(SUMPRODUCT(COUNTIF(January!$C$7:$C$86,{"Rent","Weekly shop","Bus pass","Pizza night","Weekly shop","Phone bill","To emergency fund","Streaming","Card payment","Concert tickets","Shoes"}))=0,"","Clear the example in January (step 2)")</f>
         <v>Clear the example in January (step 2)</v>
       </c>
     </row>
@@ -3805,7 +3808,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D4141AB6-1346-49BA-88EF-96A0ECAA648A}</x14:id>
+          <x14:id>{E07D84EA-FA2A-4CFE-8F93-B02BF890A21B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -3837,7 +3840,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D4141AB6-1346-49BA-88EF-96A0ECAA648A}">
+          <x14:cfRule type="dataBar" id="{E07D84EA-FA2A-4CFE-8F93-B02BF890A21B}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -5073,7 +5076,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{107B60FF-175B-4A7A-AE86-1063556FD2F5}</x14:id>
+          <x14:id>{A4C39EEF-21A2-4BBE-B370-BAD8FB4D942F}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5105,7 +5108,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{107B60FF-175B-4A7A-AE86-1063556FD2F5}">
+          <x14:cfRule type="dataBar" id="{A4C39EEF-21A2-4BBE-B370-BAD8FB4D942F}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -6341,7 +6344,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B8C56F60-D546-4C43-8A7E-7DB260E724C4}</x14:id>
+          <x14:id>{BEB9C0B4-EFE2-459E-BEB2-EFC1EA4C87AE}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -6373,7 +6376,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{B8C56F60-D546-4C43-8A7E-7DB260E724C4}">
+          <x14:cfRule type="dataBar" id="{BEB9C0B4-EFE2-459E-BEB2-EFC1EA4C87AE}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -7609,7 +7612,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3CF4652D-DCE0-4D97-B29A-325E8922BDAC}</x14:id>
+          <x14:id>{D93D6873-F82E-4AD4-A244-F9D21B99BB70}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7641,7 +7644,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3CF4652D-DCE0-4D97-B29A-325E8922BDAC}">
+          <x14:cfRule type="dataBar" id="{D93D6873-F82E-4AD4-A244-F9D21B99BB70}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8877,7 +8880,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3323BD54-9920-4662-A570-C84899F0C48B}</x14:id>
+          <x14:id>{8C34BB72-D0CD-4820-89E3-E85F4642F596}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8909,7 +8912,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3323BD54-9920-4662-A570-C84899F0C48B}">
+          <x14:cfRule type="dataBar" id="{8C34BB72-D0CD-4820-89E3-E85F4642F596}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -10145,7 +10148,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{84764CE0-206A-4C32-9D7D-187D244B5915}</x14:id>
+          <x14:id>{14A17C10-FAA2-47F9-A079-A15C71B0572E}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10177,7 +10180,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{84764CE0-206A-4C32-9D7D-187D244B5915}">
+          <x14:cfRule type="dataBar" id="{14A17C10-FAA2-47F9-A079-A15C71B0572E}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -10221,7 +10224,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10252,52 +10255,52 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>102</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>24</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O6" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P6" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q6" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10311,7 +10314,7 @@
         <v>1400</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34"/>
@@ -10337,7 +10340,7 @@
         <v>95</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34"/>
@@ -10363,7 +10366,7 @@
         <v>15.99</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -10380,7 +10383,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C10" s="25" t="n">
         <v>20</v>
@@ -10389,7 +10392,7 @@
         <v>160</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34"/>
@@ -10406,7 +10409,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C11" s="25" t="n">
         <v>22</v>
@@ -10415,7 +10418,7 @@
         <v>90</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34"/>
@@ -10441,7 +10444,7 @@
         <v>150</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F12" s="34"/>
       <c r="G12" s="34"/>
@@ -10800,7 +10803,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D32" s="23" t="n">
         <f aca="false">SUM(D7:D31)</f>
@@ -10856,12 +10859,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10892,7 +10895,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C6" s="35" t="n">
         <f aca="false">DATE(Year,1,1)+MOD(6-WEEKDAY(DATE(Year,1,1)),7)</f>
@@ -10901,39 +10904,39 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C8" s="26" t="n">
         <f aca="false">ROUND(Setup!$C$10*12/CHOOSE(MATCH($C$7,{"Weekly","Every 2 weeks","Twice a month","Monthly"},0),52,26,24,12),2)</f>
         <v>1661.54</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11583,12 +11586,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11619,15 +11622,15 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="19" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C7" s="26" t="n">
         <v>100</v>
@@ -11638,22 +11641,22 @@
         <v>8</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11684,7 +11687,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C11" s="26" t="n">
         <v>8200</v>
@@ -11862,7 +11865,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C20" s="23" t="n">
         <f aca="false">SUM(C10:C19)</f>
@@ -11920,12 +11923,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11956,22 +11959,22 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11998,7 +12001,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C8" s="26" t="n">
         <v>1800</v>
@@ -12020,7 +12023,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C9" s="26" t="n">
         <v>1200</v>
@@ -12149,7 +12152,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C39A6DE7-83A0-48D5-B57E-CC933EB7C91B}</x14:id>
+          <x14:id>{71AA7A77-EAB6-45C0-BFD0-BEE8AC647617}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12175,7 +12178,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C39A6DE7-83A0-48D5-B57E-CC933EB7C91B}">
+          <x14:cfRule type="dataBar" id="{71AA7A77-EAB6-45C0-BFD0-BEE8AC647617}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12280,11 +12283,11 @@
       </c>
       <c r="D7" s="22" t="n">
         <f aca="false">IF(COUNT(January!$E$7:$E$86)&gt;0,January!H7,"")</f>
-        <v>1992.09</v>
+        <v>2112.09</v>
       </c>
       <c r="E7" s="22" t="n">
         <f aca="false">IF(COUNT(January!$E$7:$E$86)&gt;0,January!H8,"")</f>
-        <v>1907.91</v>
+        <v>1787.91</v>
       </c>
       <c r="F7" s="22" t="n">
         <f aca="false">IF(COUNT(January!$E$7:$E$86)&gt;0,January!H9,"")</f>
@@ -12626,7 +12629,7 @@
       </c>
       <c r="I17" s="22" t="n">
         <f aca="false">IF(H17="","",SUMIFS(January!$E$7:$E$86,January!$D$7:$D$86,H17)+SUMIFS(February!$E$7:$E$86,February!$D$7:$D$86,H17)+SUMIFS(March!$E$7:$E$86,March!$D$7:$D$86,H17)+SUMIFS(April!$E$7:$E$86,April!$D$7:$D$86,H17)+SUMIFS(May!$E$7:$E$86,May!$D$7:$D$86,H17)+SUMIFS(June!$E$7:$E$86,June!$D$7:$D$86,H17)+SUMIFS(July!$E$7:$E$86,July!$D$7:$D$86,H17)+SUMIFS(August!$E$7:$E$86,August!$D$7:$D$86,H17)+SUMIFS(September!$E$7:$E$86,September!$D$7:$D$86,H17)+SUMIFS(October!$E$7:$E$86,October!$D$7:$D$86,H17)+SUMIFS(November!$E$7:$E$86,November!$D$7:$D$86,H17)+SUMIFS(December!$E$7:$E$86,December!$D$7:$D$86,H17))</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J17" s="11" t="str">
         <f aca="false">IF(H17="","",Setup!F20)</f>
@@ -12676,11 +12679,11 @@
       </c>
       <c r="D19" s="23" t="n">
         <f aca="false">SUM(D7:D18)</f>
-        <v>1992.09</v>
+        <v>2112.09</v>
       </c>
       <c r="E19" s="23" t="n">
         <f aca="false">SUM(E7:E18)</f>
-        <v>1907.91</v>
+        <v>1787.91</v>
       </c>
       <c r="F19" s="23" t="n">
         <f aca="false">SUM(F7:F18)</f>
@@ -12795,7 +12798,7 @@
       </c>
       <c r="C25" s="22" t="n">
         <f aca="false">SUMIF($J$7:$J$36,"Wants",$I$7:$I$36)</f>
-        <v>118.49</v>
+        <v>238.49</v>
       </c>
       <c r="H25" s="11" t="str">
         <f aca="false">IF(Setup!E28="","",Setup!E28)</f>
@@ -13537,7 +13540,7 @@
       </c>
       <c r="H7" s="32" t="n">
         <f aca="false">SUM(E7:E86)</f>
-        <v>1992.09</v>
+        <v>2112.09</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13558,7 +13561,7 @@
       </c>
       <c r="H8" s="32" t="n">
         <f aca="false">H6-H7</f>
-        <v>1907.91</v>
+        <v>1787.91</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13763,16 +13766,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="30" t="n">
-        <v>46412</v>
+        <v>46411</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>117</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="G16" s="11" t="str">
         <f aca="false">IF(Setup!E14="","",Setup!E14)</f>
@@ -13796,10 +13799,18 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="30"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="26"/>
+      <c r="B17" s="30" t="n">
+        <v>46412</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>64</v>
+      </c>
       <c r="G17" s="11" t="str">
         <f aca="false">IF(Setup!E15="","",Setup!E15)</f>
         <v>Phone and internet</v>
@@ -13940,15 +13951,15 @@
       </c>
       <c r="I22" s="22" t="n">
         <f aca="false">IF(G22="","",SUMIFS($E$7:$E$86,$D$7:$D$86,G22))</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J22" s="22" t="n">
         <f aca="false">IF(G22="","",H22-I22)</f>
-        <v>100</v>
+        <v>-20</v>
       </c>
       <c r="K22" s="33" t="n">
         <f aca="false">IF(OR(G22="",H22=0),"",I22/H22)</f>
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14736,7 +14747,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9951EF64-182C-43EA-93C8-2CDA19405FB7}</x14:id>
+          <x14:id>{74F8BB22-BC17-49AD-9A67-46D4F496E72D}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14768,7 +14779,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9951EF64-182C-43EA-93C8-2CDA19405FB7}">
+          <x14:cfRule type="dataBar" id="{74F8BB22-BC17-49AD-9A67-46D4F496E72D}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -16004,7 +16015,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C4CDDC1B-47FE-4291-A3FB-4795DDE5EAC1}</x14:id>
+          <x14:id>{458F88EA-3D7B-4982-92C3-893F97DDDDD7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -16036,7 +16047,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C4CDDC1B-47FE-4291-A3FB-4795DDE5EAC1}">
+          <x14:cfRule type="dataBar" id="{458F88EA-3D7B-4982-92C3-893F97DDDDD7}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -17272,7 +17283,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{AAC6B72D-3A36-4E98-8E81-88DAEB84F727}</x14:id>
+          <x14:id>{708998E1-C340-47E1-B449-9D5344B5571A}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -17304,7 +17315,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{AAC6B72D-3A36-4E98-8E81-88DAEB84F727}">
+          <x14:cfRule type="dataBar" id="{708998E1-C340-47E1-B449-9D5344B5571A}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -18540,7 +18551,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F76153D5-9DA1-4AFE-9620-F0AF2B1060FF}</x14:id>
+          <x14:id>{17C03557-6C50-4D2A-83E9-D795DD98C91F}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -18572,7 +18583,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F76153D5-9DA1-4AFE-9620-F0AF2B1060FF}">
+          <x14:cfRule type="dataBar" id="{17C03557-6C50-4D2A-83E9-D795DD98C91F}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -19808,7 +19819,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8C6C3A85-446B-4319-93FE-9846F5EF501A}</x14:id>
+          <x14:id>{C0651B90-5B3A-49A3-9E64-3EE0724EB62B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -19840,7 +19851,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8C6C3A85-446B-4319-93FE-9846F5EF501A}">
+          <x14:cfRule type="dataBar" id="{C0651B90-5B3A-49A3-9E64-3EE0724EB62B}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -21076,7 +21087,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F9D37BED-4064-48B4-8A7A-787CC08DC397}</x14:id>
+          <x14:id>{25F41094-89EE-4AEE-AE4B-93C95B4B2014}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21108,7 +21119,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F9D37BED-4064-48B4-8A7A-787CC08DC397}">
+          <x14:cfRule type="dataBar" id="{25F41094-89EE-4AEE-AE4B-93C95B4B2014}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/data/products/p-gsb-001/work/Clear-Budget.xlsx
+++ b/data/products/p-gsb-001/work/Clear-Budget.xlsx
@@ -1333,11 +1333,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="45720845"/>
-        <c:axId val="67391242"/>
+        <c:axId val="62159819"/>
+        <c:axId val="60585776"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="45720845"/>
+        <c:axId val="62159819"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1369,7 +1369,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67391242"/>
+        <c:crossAx val="60585776"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1377,7 +1377,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67391242"/>
+        <c:axId val="60585776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1419,7 +1419,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45720845"/>
+        <c:crossAx val="62159819"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1808,8 +1808,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>684720</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1037160</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>32760</xdr:rowOff>
     </xdr:to>
@@ -1839,7 +1839,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>858600</xdr:colOff>
+      <xdr:colOff>858240</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>175320</xdr:rowOff>
     </xdr:to>
@@ -1849,7 +1849,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="2185200" y="4324320"/>
+        <a:off x="2960280" y="4324320"/>
         <a:ext cx="3959640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -13460,7 +13460,8 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24"/>

--- a/data/products/p-gsb-001/work/Clear-Budget.xlsx
+++ b/data/products/p-gsb-001/work/Clear-Budget.xlsx
@@ -29,8 +29,8 @@
     <sheet name="Savings goals" sheetId="19" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
+    <definedName function="false" hidden="false" name="BudgetYear" vbProcedure="false">Setup!$C$6</definedName>
     <definedName function="false" hidden="false" name="Categories" vbProcedure="false">Setup!$E$10:$E$39</definedName>
-    <definedName function="false" hidden="false" name="Year" vbProcedure="false">Setup!$C$6</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="177">
   <si>
     <t xml:space="preserve">Clear Budget</t>
   </si>
@@ -398,6 +398,9 @@
     <t xml:space="preserve">Shoes</t>
   </si>
   <si>
+    <t xml:space="preserve">Need more than 80 rows? Review &gt; Unprotect Sheet (no password), then insert rows above the last one.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mark each bill paid with a ✓ from the dropdown.</t>
   </si>
   <si>
@@ -461,7 +464,7 @@
     <t xml:space="preserve">Paycheck plan</t>
   </si>
   <si>
-    <t xml:space="preserve">Paid weekly or every two weeks? See which bills each paycheck covers. Paid monthly? Skip this tab.</t>
+    <t xml:space="preserve">Paid weekly, every two weeks or twice a month? See which bills each paycheck covers. Paid monthly? Skip this tab.</t>
   </si>
   <si>
     <t xml:space="preserve">Next payday</t>
@@ -530,6 +533,9 @@
     <t xml:space="preserve">Interest saved</t>
   </si>
   <si>
+    <t xml:space="preserve">Medical bill</t>
+  </si>
+  <si>
     <t xml:space="preserve">Car loan</t>
   </si>
   <si>
@@ -560,6 +566,9 @@
     <t xml:space="preserve">Save per month</t>
   </si>
   <si>
+    <t xml:space="preserve">Progress bar</t>
+  </si>
+  <si>
     <t xml:space="preserve">Holiday trip</t>
   </si>
   <si>
@@ -570,17 +579,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00;[RED]&quot;-$&quot;#,##0.00;\$0.00"/>
     <numFmt numFmtId="166" formatCode="0%"/>
     <numFmt numFmtId="167" formatCode="\$#,##0"/>
     <numFmt numFmtId="168" formatCode="0"/>
     <numFmt numFmtId="169" formatCode="mmm\ d"/>
-    <numFmt numFmtId="170" formatCode="mmm\ d&quot;, &quot;yyyy"/>
-    <numFmt numFmtId="171" formatCode="ddd\ mmm\ d"/>
-    <numFmt numFmtId="172" formatCode="0.0%"/>
-    <numFmt numFmtId="173" formatCode="mmm\ yyyy"/>
+    <numFmt numFmtId="170" formatCode="General"/>
+    <numFmt numFmtId="171" formatCode="mmm\ d&quot;, &quot;yyyy"/>
+    <numFmt numFmtId="172" formatCode="ddd\ mmm\ d"/>
+    <numFmt numFmtId="173" formatCode="0.0%"/>
+    <numFmt numFmtId="174" formatCode="mmm\ yyyy"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -715,15 +725,15 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -811,7 +821,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -944,7 +954,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -952,11 +962,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="171" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -964,7 +974,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="173" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -972,9 +982,13 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="174" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1084,19 +1098,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr b="1" sz="1300" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr b="1" sz="1300" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:rPr>
               <a:t>Income and spending by month</a:t>
             </a:r>
@@ -1333,11 +1347,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="62159819"/>
-        <c:axId val="60585776"/>
+        <c:axId val="31805084"/>
+        <c:axId val="59715233"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="62159819"/>
+        <c:axId val="31805084"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1360,16 +1374,16 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60585776"/>
+        <c:crossAx val="59715233"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1377,7 +1391,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="60585776"/>
+        <c:axId val="59715233"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1410,16 +1424,16 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62159819"/>
+        <c:crossAx val="31805084"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1444,11 +1458,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
+              <a:latin typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
         </a:p>
@@ -1483,19 +1497,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr b="1" sz="1300" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr b="1" sz="1300" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
+                <a:latin typeface="Arial"/>
               </a:rPr>
               <a:t>Where the money went</a:t>
             </a:r>
@@ -1589,11 +1603,11 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                       <a:solidFill>
                         <a:srgbClr val="000000"/>
                       </a:solidFill>
-                      <a:latin typeface="Calibri"/>
+                      <a:latin typeface="Arial"/>
                     </a:defRPr>
                   </a:pPr>
                 </a:p>
@@ -1614,11 +1628,11 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                       <a:solidFill>
                         <a:srgbClr val="000000"/>
                       </a:solidFill>
-                      <a:latin typeface="Calibri"/>
+                      <a:latin typeface="Arial"/>
                     </a:defRPr>
                   </a:pPr>
                 </a:p>
@@ -1639,11 +1653,11 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                       <a:solidFill>
                         <a:srgbClr val="000000"/>
                       </a:solidFill>
-                      <a:latin typeface="Calibri"/>
+                      <a:latin typeface="Arial"/>
                     </a:defRPr>
                   </a:pPr>
                 </a:p>
@@ -1664,11 +1678,11 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                       <a:solidFill>
                         <a:srgbClr val="000000"/>
                       </a:solidFill>
-                      <a:latin typeface="Calibri"/>
+                      <a:latin typeface="Arial"/>
                     </a:defRPr>
                   </a:pPr>
                 </a:p>
@@ -1687,11 +1701,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -1771,11 +1785,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
+              <a:latin typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
         </a:p>
@@ -1811,7 +1825,7 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>1037160</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>32760</xdr:rowOff>
+      <xdr:rowOff>32400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1819,7 +1833,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="211320" y="7419960"/>
+        <a:off x="211320" y="9048600"/>
         <a:ext cx="5759640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -1840,8 +1854,8 @@
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>858240</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>175320</xdr:rowOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>42120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1849,7 +1863,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="2960280" y="4324320"/>
+        <a:off x="2960280" y="5153040"/>
         <a:ext cx="3959640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -2267,7 +2281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C13" s="10" t="s">
         <v>29</v>
       </c>
@@ -2614,7 +2628,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2664,7 +2678,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -2688,7 +2702,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -2701,7 +2715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -2714,7 +2728,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -2727,13 +2741,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -2755,7 +2769,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -2785,7 +2799,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -2815,7 +2829,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -2845,7 +2859,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -2875,7 +2889,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -2905,7 +2919,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -2935,7 +2949,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -2965,7 +2979,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -2995,7 +3009,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -3025,7 +3039,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -3055,7 +3069,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -3085,7 +3099,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -3115,7 +3129,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -3145,7 +3159,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -3175,7 +3189,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -3205,7 +3219,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -3235,7 +3249,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -3265,7 +3279,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -3295,7 +3309,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -3325,7 +3339,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -3355,7 +3369,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -3385,7 +3399,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -3415,7 +3429,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -3445,7 +3459,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -3475,7 +3489,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -3505,7 +3519,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -3535,7 +3549,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -3565,7 +3579,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -3595,7 +3609,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -3625,7 +3639,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -3655,275 +3669,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -3973,7 +3992,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -4023,7 +4042,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -4047,7 +4066,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -4060,7 +4079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -4073,7 +4092,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -4086,13 +4105,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -4114,7 +4133,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -4144,7 +4163,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -4174,7 +4193,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -4204,7 +4223,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -4234,7 +4253,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -4264,7 +4283,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -4294,7 +4313,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -4324,7 +4343,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -4354,7 +4373,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -4384,7 +4403,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -4414,7 +4433,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -4444,7 +4463,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -4474,7 +4493,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -4504,7 +4523,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -4534,7 +4553,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -4564,7 +4583,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -4594,7 +4613,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -4624,7 +4643,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -4654,7 +4673,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -4684,7 +4703,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -4714,7 +4733,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -4744,7 +4763,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -4774,7 +4793,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -4804,7 +4823,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -4834,7 +4853,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -4864,7 +4883,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -4894,7 +4913,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -4924,7 +4943,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -4954,7 +4973,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -4984,7 +5003,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -5014,275 +5033,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -5332,7 +5356,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -5382,7 +5406,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -5406,7 +5430,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -5419,7 +5443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -5432,7 +5456,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -5445,13 +5469,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -5473,7 +5497,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -5503,7 +5527,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -5533,7 +5557,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -5563,7 +5587,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -5593,7 +5617,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -5623,7 +5647,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -5653,7 +5677,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -5683,7 +5707,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -5713,7 +5737,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -5743,7 +5767,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -5773,7 +5797,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -5803,7 +5827,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -5833,7 +5857,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -5863,7 +5887,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -5893,7 +5917,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -5923,7 +5947,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -5953,7 +5977,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -5983,7 +6007,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -6013,7 +6037,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -6043,7 +6067,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -6073,7 +6097,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -6103,7 +6127,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -6133,7 +6157,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -6163,7 +6187,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -6193,7 +6217,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -6223,7 +6247,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -6253,7 +6277,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -6283,7 +6307,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -6313,7 +6337,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -6343,7 +6367,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -6373,275 +6397,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -6691,7 +6720,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -6741,7 +6770,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -6765,7 +6794,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -6778,7 +6807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -6791,7 +6820,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -6804,13 +6833,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -6832,7 +6861,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -6862,7 +6891,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -6892,7 +6921,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -6922,7 +6951,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -6952,7 +6981,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -6982,7 +7011,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -7012,7 +7041,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -7042,7 +7071,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -7072,7 +7101,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -7102,7 +7131,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -7132,7 +7161,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -7162,7 +7191,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -7192,7 +7221,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -7222,7 +7251,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -7252,7 +7281,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -7282,7 +7311,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -7312,7 +7341,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -7342,7 +7371,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -7372,7 +7401,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -7402,7 +7431,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -7432,7 +7461,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -7462,7 +7491,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -7492,7 +7521,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -7522,7 +7551,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -7552,7 +7581,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -7582,7 +7611,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -7612,7 +7641,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -7642,7 +7671,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -7672,7 +7701,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -7702,7 +7731,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -7732,275 +7761,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -8050,7 +8084,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -8100,7 +8134,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -8124,7 +8158,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -8137,7 +8171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -8150,7 +8184,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -8163,13 +8197,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -8191,7 +8225,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -8221,7 +8255,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -8251,7 +8285,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -8281,7 +8315,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -8311,7 +8345,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -8341,7 +8375,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -8371,7 +8405,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -8401,7 +8435,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -8431,7 +8465,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -8461,7 +8495,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -8491,7 +8525,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -8521,7 +8555,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -8551,7 +8585,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -8581,7 +8615,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -8611,7 +8645,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -8641,7 +8675,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -8671,7 +8705,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -8701,7 +8735,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -8731,7 +8765,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -8761,7 +8795,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -8791,7 +8825,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -8821,7 +8855,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -8851,7 +8885,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -8881,7 +8915,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -8911,7 +8945,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -8941,7 +8975,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -8971,7 +9005,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -9001,7 +9035,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -9031,7 +9065,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -9061,7 +9095,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -9091,275 +9125,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -9409,7 +9448,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -9459,7 +9498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -9483,7 +9522,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -9496,7 +9535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -9509,7 +9548,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -9522,13 +9561,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -9550,7 +9589,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -9580,7 +9619,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -9610,7 +9649,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -9640,7 +9679,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -9670,7 +9709,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -9700,7 +9739,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -9730,7 +9769,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -9760,7 +9799,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -9790,7 +9829,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -9820,7 +9859,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -9850,7 +9889,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -9880,7 +9919,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -9910,7 +9949,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -9940,7 +9979,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -9970,7 +10009,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -10000,7 +10039,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -10030,7 +10069,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -10060,7 +10099,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -10090,7 +10129,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -10120,7 +10159,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -10150,7 +10189,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -10180,7 +10219,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -10210,7 +10249,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -10240,7 +10279,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -10270,7 +10309,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -10300,7 +10339,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -10330,7 +10369,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -10360,7 +10399,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -10390,7 +10429,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -10420,7 +10459,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -10450,275 +10489,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -10787,7 +10831,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10816,54 +10860,54 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>102</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>24</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O6" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P6" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q6" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10877,7 +10921,7 @@
         <v>1400</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34"/>
@@ -10903,7 +10947,7 @@
         <v>95</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34"/>
@@ -10929,7 +10973,7 @@
         <v>15.99</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
@@ -10946,7 +10990,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C10" s="25" t="n">
         <v>20</v>
@@ -10955,7 +10999,7 @@
         <v>160</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="34"/>
@@ -10972,7 +11016,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C11" s="25" t="n">
         <v>22</v>
@@ -10981,7 +11025,7 @@
         <v>90</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="34"/>
@@ -11007,7 +11051,7 @@
         <v>150</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F12" s="34"/>
       <c r="G12" s="34"/>
@@ -11366,7 +11410,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D32" s="23" t="n">
         <f aca="false">SUM(D7:D31)</f>
@@ -11422,12 +11466,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11458,48 +11502,48 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C6" s="35" t="n">
-        <f aca="false">DATE(Year,1,1)+MOD(6-WEEKDAY(DATE(Year,1,1)),7)</f>
+        <f aca="false">DATE(BudgetYear,1,1)+MOD(6-WEEKDAY(DATE(BudgetYear,1,1)),7)</f>
         <v>46388</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C8" s="26" t="n">
         <f aca="false">ROUND(Setup!$C$10*12/CHOOSE(MATCH($C$7,{"Weekly","Every 2 weeks","Twice a month","Monthly"},0),52,26,24,12),2)</f>
         <v>1661.54</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11526,7 +11570,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="36" t="n">
-        <f aca="false">IF(F11="","",IF(F11&gt;DATE(Year,12,31),"",F11))</f>
+        <f aca="false">IF(F11="","",IF(F11&gt;DATE(BudgetYear,12,31),"",F11))</f>
         <v>46402</v>
       </c>
       <c r="C12" s="26" t="n">
@@ -11548,7 +11592,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="36" t="n">
-        <f aca="false">IF(F12="","",IF(F12&gt;DATE(Year,12,31),"",F12))</f>
+        <f aca="false">IF(F12="","",IF(F12&gt;DATE(BudgetYear,12,31),"",F12))</f>
         <v>46416</v>
       </c>
       <c r="C13" s="26" t="n">
@@ -11570,7 +11614,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="36" t="n">
-        <f aca="false">IF(F13="","",IF(F13&gt;DATE(Year,12,31),"",F13))</f>
+        <f aca="false">IF(F13="","",IF(F13&gt;DATE(BudgetYear,12,31),"",F13))</f>
         <v>46430</v>
       </c>
       <c r="C14" s="26" t="n">
@@ -11592,7 +11636,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="36" t="n">
-        <f aca="false">IF(F14="","",IF(F14&gt;DATE(Year,12,31),"",F14))</f>
+        <f aca="false">IF(F14="","",IF(F14&gt;DATE(BudgetYear,12,31),"",F14))</f>
         <v>46444</v>
       </c>
       <c r="C15" s="26" t="n">
@@ -11614,7 +11658,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="36" t="n">
-        <f aca="false">IF(F15="","",IF(F15&gt;DATE(Year,12,31),"",F15))</f>
+        <f aca="false">IF(F15="","",IF(F15&gt;DATE(BudgetYear,12,31),"",F15))</f>
         <v>46458</v>
       </c>
       <c r="C16" s="26" t="n">
@@ -11636,7 +11680,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="36" t="n">
-        <f aca="false">IF(F16="","",IF(F16&gt;DATE(Year,12,31),"",F16))</f>
+        <f aca="false">IF(F16="","",IF(F16&gt;DATE(BudgetYear,12,31),"",F16))</f>
         <v>46472</v>
       </c>
       <c r="C17" s="26" t="n">
@@ -11658,7 +11702,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="36" t="n">
-        <f aca="false">IF(F17="","",IF(F17&gt;DATE(Year,12,31),"",F17))</f>
+        <f aca="false">IF(F17="","",IF(F17&gt;DATE(BudgetYear,12,31),"",F17))</f>
         <v>46486</v>
       </c>
       <c r="C18" s="26" t="n">
@@ -11680,7 +11724,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="36" t="n">
-        <f aca="false">IF(F18="","",IF(F18&gt;DATE(Year,12,31),"",F18))</f>
+        <f aca="false">IF(F18="","",IF(F18&gt;DATE(BudgetYear,12,31),"",F18))</f>
         <v>46500</v>
       </c>
       <c r="C19" s="26" t="n">
@@ -11702,7 +11746,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="36" t="n">
-        <f aca="false">IF(F19="","",IF(F19&gt;DATE(Year,12,31),"",F19))</f>
+        <f aca="false">IF(F19="","",IF(F19&gt;DATE(BudgetYear,12,31),"",F19))</f>
         <v>46514</v>
       </c>
       <c r="C20" s="26" t="n">
@@ -11724,7 +11768,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="36" t="n">
-        <f aca="false">IF(F20="","",IF(F20&gt;DATE(Year,12,31),"",F20))</f>
+        <f aca="false">IF(F20="","",IF(F20&gt;DATE(BudgetYear,12,31),"",F20))</f>
         <v>46528</v>
       </c>
       <c r="C21" s="26" t="n">
@@ -11746,7 +11790,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="36" t="n">
-        <f aca="false">IF(F21="","",IF(F21&gt;DATE(Year,12,31),"",F21))</f>
+        <f aca="false">IF(F21="","",IF(F21&gt;DATE(BudgetYear,12,31),"",F21))</f>
         <v>46542</v>
       </c>
       <c r="C22" s="26" t="n">
@@ -11768,7 +11812,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="36" t="n">
-        <f aca="false">IF(F22="","",IF(F22&gt;DATE(Year,12,31),"",F22))</f>
+        <f aca="false">IF(F22="","",IF(F22&gt;DATE(BudgetYear,12,31),"",F22))</f>
         <v>46556</v>
       </c>
       <c r="C23" s="26" t="n">
@@ -11790,7 +11834,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="36" t="n">
-        <f aca="false">IF(F23="","",IF(F23&gt;DATE(Year,12,31),"",F23))</f>
+        <f aca="false">IF(F23="","",IF(F23&gt;DATE(BudgetYear,12,31),"",F23))</f>
         <v>46570</v>
       </c>
       <c r="C24" s="26" t="n">
@@ -11812,7 +11856,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="36" t="n">
-        <f aca="false">IF(F24="","",IF(F24&gt;DATE(Year,12,31),"",F24))</f>
+        <f aca="false">IF(F24="","",IF(F24&gt;DATE(BudgetYear,12,31),"",F24))</f>
         <v>46584</v>
       </c>
       <c r="C25" s="26" t="n">
@@ -11834,7 +11878,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="36" t="n">
-        <f aca="false">IF(F25="","",IF(F25&gt;DATE(Year,12,31),"",F25))</f>
+        <f aca="false">IF(F25="","",IF(F25&gt;DATE(BudgetYear,12,31),"",F25))</f>
         <v>46598</v>
       </c>
       <c r="C26" s="26" t="n">
@@ -11856,7 +11900,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="36" t="n">
-        <f aca="false">IF(F26="","",IF(F26&gt;DATE(Year,12,31),"",F26))</f>
+        <f aca="false">IF(F26="","",IF(F26&gt;DATE(BudgetYear,12,31),"",F26))</f>
         <v>46612</v>
       </c>
       <c r="C27" s="26" t="n">
@@ -11878,7 +11922,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="36" t="n">
-        <f aca="false">IF(F27="","",IF(F27&gt;DATE(Year,12,31),"",F27))</f>
+        <f aca="false">IF(F27="","",IF(F27&gt;DATE(BudgetYear,12,31),"",F27))</f>
         <v>46626</v>
       </c>
       <c r="C28" s="26" t="n">
@@ -11900,7 +11944,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="36" t="n">
-        <f aca="false">IF(F28="","",IF(F28&gt;DATE(Year,12,31),"",F28))</f>
+        <f aca="false">IF(F28="","",IF(F28&gt;DATE(BudgetYear,12,31),"",F28))</f>
         <v>46640</v>
       </c>
       <c r="C29" s="26" t="n">
@@ -11922,7 +11966,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="36" t="n">
-        <f aca="false">IF(F29="","",IF(F29&gt;DATE(Year,12,31),"",F29))</f>
+        <f aca="false">IF(F29="","",IF(F29&gt;DATE(BudgetYear,12,31),"",F29))</f>
         <v>46654</v>
       </c>
       <c r="C30" s="26" t="n">
@@ -11944,7 +11988,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="36" t="n">
-        <f aca="false">IF(F30="","",IF(F30&gt;DATE(Year,12,31),"",F30))</f>
+        <f aca="false">IF(F30="","",IF(F30&gt;DATE(BudgetYear,12,31),"",F30))</f>
         <v>46668</v>
       </c>
       <c r="C31" s="26" t="n">
@@ -11966,7 +12010,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="36" t="n">
-        <f aca="false">IF(F31="","",IF(F31&gt;DATE(Year,12,31),"",F31))</f>
+        <f aca="false">IF(F31="","",IF(F31&gt;DATE(BudgetYear,12,31),"",F31))</f>
         <v>46682</v>
       </c>
       <c r="C32" s="26" t="n">
@@ -11988,7 +12032,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="36" t="n">
-        <f aca="false">IF(F32="","",IF(F32&gt;DATE(Year,12,31),"",F32))</f>
+        <f aca="false">IF(F32="","",IF(F32&gt;DATE(BudgetYear,12,31),"",F32))</f>
         <v>46696</v>
       </c>
       <c r="C33" s="26" t="n">
@@ -12010,7 +12054,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="36" t="n">
-        <f aca="false">IF(F33="","",IF(F33&gt;DATE(Year,12,31),"",F33))</f>
+        <f aca="false">IF(F33="","",IF(F33&gt;DATE(BudgetYear,12,31),"",F33))</f>
         <v>46710</v>
       </c>
       <c r="C34" s="26" t="n">
@@ -12032,7 +12076,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="36" t="n">
-        <f aca="false">IF(F34="","",IF(F34&gt;DATE(Year,12,31),"",F34))</f>
+        <f aca="false">IF(F34="","",IF(F34&gt;DATE(BudgetYear,12,31),"",F34))</f>
         <v>46724</v>
       </c>
       <c r="C35" s="26" t="n">
@@ -12054,7 +12098,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="36" t="n">
-        <f aca="false">IF(F35="","",IF(F35&gt;DATE(Year,12,31),"",F35))</f>
+        <f aca="false">IF(F35="","",IF(F35&gt;DATE(BudgetYear,12,31),"",F35))</f>
         <v>46738</v>
       </c>
       <c r="C36" s="26" t="n">
@@ -12076,7 +12120,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="36" t="n">
-        <f aca="false">IF(F36="","",IF(F36&gt;DATE(Year,12,31),"",F36))</f>
+        <f aca="false">IF(F36="","",IF(F36&gt;DATE(BudgetYear,12,31),"",F36))</f>
         <v>46752</v>
       </c>
       <c r="C37" s="26" t="n">
@@ -12098,7 +12142,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="36" t="str">
-        <f aca="false">IF(F37="","",IF(F37&gt;DATE(Year,12,31),"",F37))</f>
+        <f aca="false">IF(F37="","",IF(F37&gt;DATE(BudgetYear,12,31),"",F37))</f>
         <v/>
       </c>
       <c r="C38" s="26" t="str">
@@ -12120,7 +12164,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="36" t="str">
-        <f aca="false">IF(F38="","",IF(F38&gt;DATE(Year,12,31),"",F38))</f>
+        <f aca="false">IF(F38="","",IF(F38&gt;DATE(BudgetYear,12,31),"",F38))</f>
         <v/>
       </c>
       <c r="C39" s="26" t="str">
@@ -12142,7 +12186,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="36" t="str">
-        <f aca="false">IF(F39="","",IF(F39&gt;DATE(Year,12,31),"",F39))</f>
+        <f aca="false">IF(F39="","",IF(F39&gt;DATE(BudgetYear,12,31),"",F39))</f>
         <v/>
       </c>
       <c r="C40" s="26" t="str">
@@ -12164,7 +12208,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="36" t="str">
-        <f aca="false">IF(F40="","",IF(F40&gt;DATE(Year,12,31),"",F40))</f>
+        <f aca="false">IF(F40="","",IF(F40&gt;DATE(BudgetYear,12,31),"",F40))</f>
         <v/>
       </c>
       <c r="C41" s="26" t="str">
@@ -12186,7 +12230,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="36" t="str">
-        <f aca="false">IF(F41="","",IF(F41&gt;DATE(Year,12,31),"",F41))</f>
+        <f aca="false">IF(F41="","",IF(F41&gt;DATE(BudgetYear,12,31),"",F41))</f>
         <v/>
       </c>
       <c r="C42" s="26" t="str">
@@ -12208,7 +12252,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="36" t="str">
-        <f aca="false">IF(F42="","",IF(F42&gt;DATE(Year,12,31),"",F42))</f>
+        <f aca="false">IF(F42="","",IF(F42&gt;DATE(BudgetYear,12,31),"",F42))</f>
         <v/>
       </c>
       <c r="C43" s="26" t="str">
@@ -12230,7 +12274,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="36" t="str">
-        <f aca="false">IF(F43="","",IF(F43&gt;DATE(Year,12,31),"",F43))</f>
+        <f aca="false">IF(F43="","",IF(F43&gt;DATE(BudgetYear,12,31),"",F43))</f>
         <v/>
       </c>
       <c r="C44" s="26" t="str">
@@ -12252,7 +12296,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="36" t="str">
-        <f aca="false">IF(F44="","",IF(F44&gt;DATE(Year,12,31),"",F44))</f>
+        <f aca="false">IF(F44="","",IF(F44&gt;DATE(BudgetYear,12,31),"",F44))</f>
         <v/>
       </c>
       <c r="C45" s="26" t="str">
@@ -12274,7 +12318,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="36" t="str">
-        <f aca="false">IF(F45="","",IF(F45&gt;DATE(Year,12,31),"",F45))</f>
+        <f aca="false">IF(F45="","",IF(F45&gt;DATE(BudgetYear,12,31),"",F45))</f>
         <v/>
       </c>
       <c r="C46" s="26" t="str">
@@ -12296,7 +12340,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="36" t="str">
-        <f aca="false">IF(F46="","",IF(F46&gt;DATE(Year,12,31),"",F46))</f>
+        <f aca="false">IF(F46="","",IF(F46&gt;DATE(BudgetYear,12,31),"",F46))</f>
         <v/>
       </c>
       <c r="C47" s="26" t="str">
@@ -12318,7 +12362,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="36" t="str">
-        <f aca="false">IF(F47="","",IF(F47&gt;DATE(Year,12,31),"",F47))</f>
+        <f aca="false">IF(F47="","",IF(F47&gt;DATE(BudgetYear,12,31),"",F47))</f>
         <v/>
       </c>
       <c r="C48" s="26" t="str">
@@ -12340,7 +12384,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="36" t="str">
-        <f aca="false">IF(F48="","",IF(F48&gt;DATE(Year,12,31),"",F48))</f>
+        <f aca="false">IF(F48="","",IF(F48&gt;DATE(BudgetYear,12,31),"",F48))</f>
         <v/>
       </c>
       <c r="C49" s="26" t="str">
@@ -12362,7 +12406,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="36" t="str">
-        <f aca="false">IF(F49="","",IF(F49&gt;DATE(Year,12,31),"",F49))</f>
+        <f aca="false">IF(F49="","",IF(F49&gt;DATE(BudgetYear,12,31),"",F49))</f>
         <v/>
       </c>
       <c r="C50" s="26" t="str">
@@ -12384,7 +12428,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="36" t="str">
-        <f aca="false">IF(F50="","",IF(F50&gt;DATE(Year,12,31),"",F50))</f>
+        <f aca="false">IF(F50="","",IF(F50&gt;DATE(BudgetYear,12,31),"",F50))</f>
         <v/>
       </c>
       <c r="C51" s="26" t="str">
@@ -12406,7 +12450,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="36" t="str">
-        <f aca="false">IF(F51="","",IF(F51&gt;DATE(Year,12,31),"",F51))</f>
+        <f aca="false">IF(F51="","",IF(F51&gt;DATE(BudgetYear,12,31),"",F51))</f>
         <v/>
       </c>
       <c r="C52" s="26" t="str">
@@ -12428,7 +12472,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="36" t="str">
-        <f aca="false">IF(F52="","",IF(F52&gt;DATE(Year,12,31),"",F52))</f>
+        <f aca="false">IF(F52="","",IF(F52&gt;DATE(BudgetYear,12,31),"",F52))</f>
         <v/>
       </c>
       <c r="C53" s="26" t="str">
@@ -12450,7 +12494,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="36" t="str">
-        <f aca="false">IF(F53="","",IF(F53&gt;DATE(Year,12,31),"",F53))</f>
+        <f aca="false">IF(F53="","",IF(F53&gt;DATE(BudgetYear,12,31),"",F53))</f>
         <v/>
       </c>
       <c r="C54" s="26" t="str">
@@ -12472,7 +12516,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="36" t="str">
-        <f aca="false">IF(F54="","",IF(F54&gt;DATE(Year,12,31),"",F54))</f>
+        <f aca="false">IF(F54="","",IF(F54&gt;DATE(BudgetYear,12,31),"",F54))</f>
         <v/>
       </c>
       <c r="C55" s="26" t="str">
@@ -12494,7 +12538,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="36" t="str">
-        <f aca="false">IF(F55="","",IF(F55&gt;DATE(Year,12,31),"",F55))</f>
+        <f aca="false">IF(F55="","",IF(F55&gt;DATE(BudgetYear,12,31),"",F55))</f>
         <v/>
       </c>
       <c r="C56" s="26" t="str">
@@ -12516,7 +12560,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="36" t="str">
-        <f aca="false">IF(F56="","",IF(F56&gt;DATE(Year,12,31),"",F56))</f>
+        <f aca="false">IF(F56="","",IF(F56&gt;DATE(BudgetYear,12,31),"",F56))</f>
         <v/>
       </c>
       <c r="C57" s="26" t="str">
@@ -12538,7 +12582,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="36" t="str">
-        <f aca="false">IF(F57="","",IF(F57&gt;DATE(Year,12,31),"",F57))</f>
+        <f aca="false">IF(F57="","",IF(F57&gt;DATE(BudgetYear,12,31),"",F57))</f>
         <v/>
       </c>
       <c r="C58" s="26" t="str">
@@ -12560,7 +12604,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="36" t="str">
-        <f aca="false">IF(F58="","",IF(F58&gt;DATE(Year,12,31),"",F58))</f>
+        <f aca="false">IF(F58="","",IF(F58&gt;DATE(BudgetYear,12,31),"",F58))</f>
         <v/>
       </c>
       <c r="C59" s="26" t="str">
@@ -12582,7 +12626,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="36" t="str">
-        <f aca="false">IF(F59="","",IF(F59&gt;DATE(Year,12,31),"",F59))</f>
+        <f aca="false">IF(F59="","",IF(F59&gt;DATE(BudgetYear,12,31),"",F59))</f>
         <v/>
       </c>
       <c r="C60" s="26" t="str">
@@ -12604,7 +12648,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="36" t="str">
-        <f aca="false">IF(F60="","",IF(F60&gt;DATE(Year,12,31),"",F60))</f>
+        <f aca="false">IF(F60="","",IF(F60&gt;DATE(BudgetYear,12,31),"",F60))</f>
         <v/>
       </c>
       <c r="C61" s="26" t="str">
@@ -12626,7 +12670,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="36" t="str">
-        <f aca="false">IF(F61="","",IF(F61&gt;DATE(Year,12,31),"",F61))</f>
+        <f aca="false">IF(F61="","",IF(F61&gt;DATE(BudgetYear,12,31),"",F61))</f>
         <v/>
       </c>
       <c r="C62" s="26" t="str">
@@ -12648,7 +12692,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="36" t="str">
-        <f aca="false">IF(F62="","",IF(F62&gt;DATE(Year,12,31),"",F62))</f>
+        <f aca="false">IF(F62="","",IF(F62&gt;DATE(BudgetYear,12,31),"",F62))</f>
         <v/>
       </c>
       <c r="C63" s="26" t="str">
@@ -12670,7 +12714,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="36" t="str">
-        <f aca="false">IF(F63="","",IF(F63&gt;DATE(Year,12,31),"",F63))</f>
+        <f aca="false">IF(F63="","",IF(F63&gt;DATE(BudgetYear,12,31),"",F63))</f>
         <v/>
       </c>
       <c r="C64" s="26" t="str">
@@ -12736,20 +12780,21 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="11" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12780,64 +12825,64 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="19" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C7" s="26" t="n">
         <v>100</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="17" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="C10" s="26" t="n">
-        <v>2400</v>
+        <v>600</v>
       </c>
       <c r="D10" s="38" t="n">
-        <v>0.2299</v>
+        <v>0</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F10" s="39" t="n">
         <f aca="false">IF(C10="","",IF($C$6="Snowball",COUNTIFS($C$10:$C$19,"&lt;"&amp;C10,$C$10:$C$19,"&lt;&gt;")+1,COUNTIFS($D$10:$D$19,"&gt;"&amp;D10,$C$10:$C$19,"&lt;&gt;")+1))</f>
@@ -12845,33 +12890,33 @@
       </c>
       <c r="G10" s="39" t="n">
         <f aca="false">IF(OR(C10="",E10=""),"",IFERROR(ROUNDUP(NPER(D10/12,-E10,C10),0),"never: raise the minimum"))</f>
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="H10" s="22" t="n">
         <f aca="false">IF(OR(C10="",E10="",NOT(ISNUMBER(G10))),"",G10*E10-C10)</f>
-        <v>1425</v>
+        <v>0</v>
       </c>
       <c r="I10" s="39" t="n">
         <f aca="false">IF(OR(C10="",E10="",F10&lt;&gt;1),"",IFERROR(ROUNDUP(NPER(D10/12,-(E10+$C$7),C10),0),""))</f>
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J10" s="22" t="n">
         <f aca="false">IF(OR(I10="",NOT(ISNUMBER(H10))),"",MAX(0,H10-(I10*(E10+$C$7)-C10)))</f>
-        <v>850</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="17" t="s">
-        <v>162</v>
+        <v>95</v>
       </c>
       <c r="C11" s="26" t="n">
-        <v>8200</v>
+        <v>2400</v>
       </c>
       <c r="D11" s="38" t="n">
-        <v>0.069</v>
+        <v>0.2299</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="F11" s="39" t="n">
         <f aca="false">IF(C11="","",IF($C$6="Snowball",COUNTIFS($C$10:$C$19,"&lt;"&amp;C11,$C$10:$C$19,"&lt;&gt;")+1,COUNTIFS($D$10:$D$19,"&gt;"&amp;D11,$C$10:$C$19,"&lt;&gt;")+1))</f>
@@ -12879,11 +12924,11 @@
       </c>
       <c r="G11" s="39" t="n">
         <f aca="false">IF(OR(C11="",E11=""),"",IFERROR(ROUNDUP(NPER(D11/12,-E11,C11),0),"never: raise the minimum"))</f>
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H11" s="22" t="n">
         <f aca="false">IF(OR(C11="",E11="",NOT(ISNUMBER(G11))),"",G11*E11-C11)</f>
-        <v>1250</v>
+        <v>1425</v>
       </c>
       <c r="I11" s="39" t="str">
         <f aca="false">IF(OR(C11="",E11="",F11&lt;&gt;1),"",IFERROR(ROUNDUP(NPER(D11/12,-(E11+$C$7),C11),0),""))</f>
@@ -12896,16 +12941,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="17" t="s">
-        <v>96</v>
+        <v>164</v>
       </c>
       <c r="C12" s="26" t="n">
-        <v>14500</v>
+        <v>8200</v>
       </c>
       <c r="D12" s="38" t="n">
-        <v>0.055</v>
+        <v>0.069</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="F12" s="39" t="n">
         <f aca="false">IF(C12="","",IF($C$6="Snowball",COUNTIFS($C$10:$C$19,"&lt;"&amp;C12,$C$10:$C$19,"&lt;&gt;")+1,COUNTIFS($D$10:$D$19,"&gt;"&amp;D12,$C$10:$C$19,"&lt;&gt;")+1))</f>
@@ -12913,11 +12958,11 @@
       </c>
       <c r="G12" s="39" t="n">
         <f aca="false">IF(OR(C12="",E12=""),"",IFERROR(ROUNDUP(NPER(D12/12,-E12,C12),0),"never: raise the minimum"))</f>
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="H12" s="22" t="n">
         <f aca="false">IF(OR(C12="",E12="",NOT(ISNUMBER(G12))),"",G12*E12-C12)</f>
-        <v>3680</v>
+        <v>1250</v>
       </c>
       <c r="I12" s="39" t="str">
         <f aca="false">IF(OR(C12="",E12="",F12&lt;&gt;1),"",IFERROR(ROUNDUP(NPER(D12/12,-(E12+$C$7),C12),0),""))</f>
@@ -12929,21 +12974,29 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="17"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="39" t="str">
+      <c r="B13" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="26" t="n">
+        <v>14500</v>
+      </c>
+      <c r="D13" s="38" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>180</v>
+      </c>
+      <c r="F13" s="39" t="n">
         <f aca="false">IF(C13="","",IF($C$6="Snowball",COUNTIFS($C$10:$C$19,"&lt;"&amp;C13,$C$10:$C$19,"&lt;&gt;")+1,COUNTIFS($D$10:$D$19,"&gt;"&amp;D13,$C$10:$C$19,"&lt;&gt;")+1))</f>
-        <v/>
-      </c>
-      <c r="G13" s="39" t="str">
+        <v>4</v>
+      </c>
+      <c r="G13" s="39" t="n">
         <f aca="false">IF(OR(C13="",E13=""),"",IFERROR(ROUNDUP(NPER(D13/12,-E13,C13),0),"never: raise the minimum"))</f>
-        <v/>
-      </c>
-      <c r="H13" s="22" t="str">
+        <v>101</v>
+      </c>
+      <c r="H13" s="22" t="n">
         <f aca="false">IF(OR(C13="",E13="",NOT(ISNUMBER(G13))),"",G13*E13-C13)</f>
-        <v/>
+        <v>3680</v>
       </c>
       <c r="I13" s="39" t="str">
         <f aca="false">IF(OR(C13="",E13="",F13&lt;&gt;1),"",IFERROR(ROUNDUP(NPER(D13/12,-(E13+$C$7),C13),0),""))</f>
@@ -13112,15 +13165,15 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="19" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C20" s="23" t="n">
         <f aca="false">SUM(C10:C19)</f>
-        <v>25100</v>
+        <v>25700</v>
       </c>
       <c r="E20" s="23" t="n">
         <f aca="false">SUM(E10:E19)</f>
-        <v>465</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -13170,12 +13223,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13204,26 +13257,28 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="H6" s="10"/>
+        <v>173</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="17" t="s">
@@ -13243,17 +13298,17 @@
         <v>46722</v>
       </c>
       <c r="G7" s="22" t="n">
-        <f aca="true">IF(OR(C7="",F7=""),"",IF(D7&gt;=C7,"Reached",IF(((YEAR(F7)-YEAR(TODAY()))*12+MONTH(F7)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C7-D7)/((YEAR(F7)-YEAR(TODAY()))*12+MONTH(F7)-MONTH(TODAY())))))</f>
+        <f aca="true">IF(OR(C7="",F7=""),"",IF(D7&gt;=C7,"Reached",IF(((YEAR(F7)-YEAR(TODAY()))*12+MONTH(F7)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C7-D7)/MAX(1,((YEAR(F7)-YEAR(TODAY()))*12+MONTH(F7)-MONTH(TODAY()))))))</f>
         <v>271.428571428571</v>
       </c>
-      <c r="H7" s="33" t="str">
+      <c r="H7" s="41" t="str">
         <f aca="false">IF(E7="","",REPT("█",ROUND(MIN(1,MAX(0,E7))*10,0))&amp;REPT("░",10-ROUND(MIN(1,MAX(0,E7))*10,0)))</f>
         <v>██░░░░░░░░</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="17" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C8" s="26" t="n">
         <v>1800</v>
@@ -13269,17 +13324,17 @@
         <v>46569</v>
       </c>
       <c r="G8" s="22" t="n">
-        <f aca="true">IF(OR(C8="",F8=""),"",IF(D8&gt;=C8,"Reached",IF(((YEAR(F8)-YEAR(TODAY()))*12+MONTH(F8)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C8-D8)/((YEAR(F8)-YEAR(TODAY()))*12+MONTH(F8)-MONTH(TODAY())))))</f>
+        <f aca="true">IF(OR(C8="",F8=""),"",IF(D8&gt;=C8,"Reached",IF(((YEAR(F8)-YEAR(TODAY()))*12+MONTH(F8)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C8-D8)/MAX(1,((YEAR(F8)-YEAR(TODAY()))*12+MONTH(F8)-MONTH(TODAY()))))))</f>
         <v>150</v>
       </c>
-      <c r="H8" s="33" t="str">
+      <c r="H8" s="41" t="str">
         <f aca="false">IF(E8="","",REPT("█",ROUND(MIN(1,MAX(0,E8))*10,0))&amp;REPT("░",10-ROUND(MIN(1,MAX(0,E8))*10,0)))</f>
         <v>███░░░░░░░</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="17" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C9" s="26" t="n">
         <v>1200</v>
@@ -13295,10 +13350,10 @@
         <v>46631</v>
       </c>
       <c r="G9" s="22" t="n">
-        <f aca="true">IF(OR(C9="",F9=""),"",IF(D9&gt;=C9,"Reached",IF(((YEAR(F9)-YEAR(TODAY()))*12+MONTH(F9)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C9-D9)/((YEAR(F9)-YEAR(TODAY()))*12+MONTH(F9)-MONTH(TODAY())))))</f>
+        <f aca="true">IF(OR(C9="",F9=""),"",IF(D9&gt;=C9,"Reached",IF(((YEAR(F9)-YEAR(TODAY()))*12+MONTH(F9)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C9-D9)/MAX(1,((YEAR(F9)-YEAR(TODAY()))*12+MONTH(F9)-MONTH(TODAY()))))))</f>
         <v>81.8181818181818</v>
       </c>
-      <c r="H9" s="33" t="str">
+      <c r="H9" s="41" t="str">
         <f aca="false">IF(E9="","",REPT("█",ROUND(MIN(1,MAX(0,E9))*10,0))&amp;REPT("░",10-ROUND(MIN(1,MAX(0,E9))*10,0)))</f>
         <v>███░░░░░░░</v>
       </c>
@@ -13313,10 +13368,10 @@
       </c>
       <c r="F10" s="40"/>
       <c r="G10" s="22" t="str">
-        <f aca="true">IF(OR(C10="",F10=""),"",IF(D10&gt;=C10,"Reached",IF(((YEAR(F10)-YEAR(TODAY()))*12+MONTH(F10)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C10-D10)/((YEAR(F10)-YEAR(TODAY()))*12+MONTH(F10)-MONTH(TODAY())))))</f>
-        <v/>
-      </c>
-      <c r="H10" s="33" t="str">
+        <f aca="true">IF(OR(C10="",F10=""),"",IF(D10&gt;=C10,"Reached",IF(((YEAR(F10)-YEAR(TODAY()))*12+MONTH(F10)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C10-D10)/MAX(1,((YEAR(F10)-YEAR(TODAY()))*12+MONTH(F10)-MONTH(TODAY()))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="41" t="str">
         <f aca="false">IF(E10="","",REPT("█",ROUND(MIN(1,MAX(0,E10))*10,0))&amp;REPT("░",10-ROUND(MIN(1,MAX(0,E10))*10,0)))</f>
         <v/>
       </c>
@@ -13331,10 +13386,10 @@
       </c>
       <c r="F11" s="40"/>
       <c r="G11" s="22" t="str">
-        <f aca="true">IF(OR(C11="",F11=""),"",IF(D11&gt;=C11,"Reached",IF(((YEAR(F11)-YEAR(TODAY()))*12+MONTH(F11)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C11-D11)/((YEAR(F11)-YEAR(TODAY()))*12+MONTH(F11)-MONTH(TODAY())))))</f>
-        <v/>
-      </c>
-      <c r="H11" s="33" t="str">
+        <f aca="true">IF(OR(C11="",F11=""),"",IF(D11&gt;=C11,"Reached",IF(((YEAR(F11)-YEAR(TODAY()))*12+MONTH(F11)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C11-D11)/MAX(1,((YEAR(F11)-YEAR(TODAY()))*12+MONTH(F11)-MONTH(TODAY()))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="41" t="str">
         <f aca="false">IF(E11="","",REPT("█",ROUND(MIN(1,MAX(0,E11))*10,0))&amp;REPT("░",10-ROUND(MIN(1,MAX(0,E11))*10,0)))</f>
         <v/>
       </c>
@@ -13349,10 +13404,10 @@
       </c>
       <c r="F12" s="40"/>
       <c r="G12" s="22" t="str">
-        <f aca="true">IF(OR(C12="",F12=""),"",IF(D12&gt;=C12,"Reached",IF(((YEAR(F12)-YEAR(TODAY()))*12+MONTH(F12)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C12-D12)/((YEAR(F12)-YEAR(TODAY()))*12+MONTH(F12)-MONTH(TODAY())))))</f>
-        <v/>
-      </c>
-      <c r="H12" s="33" t="str">
+        <f aca="true">IF(OR(C12="",F12=""),"",IF(D12&gt;=C12,"Reached",IF(((YEAR(F12)-YEAR(TODAY()))*12+MONTH(F12)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C12-D12)/MAX(1,((YEAR(F12)-YEAR(TODAY()))*12+MONTH(F12)-MONTH(TODAY()))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="41" t="str">
         <f aca="false">IF(E12="","",REPT("█",ROUND(MIN(1,MAX(0,E12))*10,0))&amp;REPT("░",10-ROUND(MIN(1,MAX(0,E12))*10,0)))</f>
         <v/>
       </c>
@@ -13367,10 +13422,10 @@
       </c>
       <c r="F13" s="40"/>
       <c r="G13" s="22" t="str">
-        <f aca="true">IF(OR(C13="",F13=""),"",IF(D13&gt;=C13,"Reached",IF(((YEAR(F13)-YEAR(TODAY()))*12+MONTH(F13)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C13-D13)/((YEAR(F13)-YEAR(TODAY()))*12+MONTH(F13)-MONTH(TODAY())))))</f>
-        <v/>
-      </c>
-      <c r="H13" s="33" t="str">
+        <f aca="true">IF(OR(C13="",F13=""),"",IF(D13&gt;=C13,"Reached",IF(((YEAR(F13)-YEAR(TODAY()))*12+MONTH(F13)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C13-D13)/MAX(1,((YEAR(F13)-YEAR(TODAY()))*12+MONTH(F13)-MONTH(TODAY()))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="41" t="str">
         <f aca="false">IF(E13="","",REPT("█",ROUND(MIN(1,MAX(0,E13))*10,0))&amp;REPT("░",10-ROUND(MIN(1,MAX(0,E13))*10,0)))</f>
         <v/>
       </c>
@@ -13385,10 +13440,10 @@
       </c>
       <c r="F14" s="40"/>
       <c r="G14" s="22" t="str">
-        <f aca="true">IF(OR(C14="",F14=""),"",IF(D14&gt;=C14,"Reached",IF(((YEAR(F14)-YEAR(TODAY()))*12+MONTH(F14)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C14-D14)/((YEAR(F14)-YEAR(TODAY()))*12+MONTH(F14)-MONTH(TODAY())))))</f>
-        <v/>
-      </c>
-      <c r="H14" s="33" t="str">
+        <f aca="true">IF(OR(C14="",F14=""),"",IF(D14&gt;=C14,"Reached",IF(((YEAR(F14)-YEAR(TODAY()))*12+MONTH(F14)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C14-D14)/MAX(1,((YEAR(F14)-YEAR(TODAY()))*12+MONTH(F14)-MONTH(TODAY()))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="41" t="str">
         <f aca="false">IF(E14="","",REPT("█",ROUND(MIN(1,MAX(0,E14))*10,0))&amp;REPT("░",10-ROUND(MIN(1,MAX(0,E14))*10,0)))</f>
         <v/>
       </c>
@@ -13403,10 +13458,10 @@
       </c>
       <c r="F15" s="40"/>
       <c r="G15" s="22" t="str">
-        <f aca="true">IF(OR(C15="",F15=""),"",IF(D15&gt;=C15,"Reached",IF(((YEAR(F15)-YEAR(TODAY()))*12+MONTH(F15)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C15-D15)/((YEAR(F15)-YEAR(TODAY()))*12+MONTH(F15)-MONTH(TODAY())))))</f>
-        <v/>
-      </c>
-      <c r="H15" s="33" t="str">
+        <f aca="true">IF(OR(C15="",F15=""),"",IF(D15&gt;=C15,"Reached",IF(((YEAR(F15)-YEAR(TODAY()))*12+MONTH(F15)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C15-D15)/MAX(1,((YEAR(F15)-YEAR(TODAY()))*12+MONTH(F15)-MONTH(TODAY()))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="41" t="str">
         <f aca="false">IF(E15="","",REPT("█",ROUND(MIN(1,MAX(0,E15))*10,0))&amp;REPT("░",10-ROUND(MIN(1,MAX(0,E15))*10,0)))</f>
         <v/>
       </c>
@@ -13421,10 +13476,10 @@
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="22" t="str">
-        <f aca="true">IF(OR(C16="",F16=""),"",IF(D16&gt;=C16,"Reached",IF(((YEAR(F16)-YEAR(TODAY()))*12+MONTH(F16)-MONTH(TODAY()))&lt;1,"Date passed: pick a new one",(C16-D16)/((YEAR(F16)-YEAR(TODAY()))*12+MONTH(F16)-MONTH(TODAY())))))</f>
-        <v/>
-      </c>
-      <c r="H16" s="33" t="str">
+        <f aca="true">IF(OR(C16="",F16=""),"",IF(D16&gt;=C16,"Reached",IF(((YEAR(F16)-YEAR(TODAY()))*12+MONTH(F16)-MONTH(TODAY()))&lt;0,"Date passed: pick a new one",(C16-D16)/MAX(1,((YEAR(F16)-YEAR(TODAY()))*12+MONTH(F16)-MONTH(TODAY()))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="41" t="str">
         <f aca="false">IF(E16="","",REPT("█",ROUND(MIN(1,MAX(0,E16))*10,0))&amp;REPT("░",10-ROUND(MIN(1,MAX(0,E16))*10,0)))</f>
         <v/>
       </c>
@@ -13506,7 +13561,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>59</v>
       </c>
@@ -13529,7 +13584,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="21" t="s">
         <v>12</v>
       </c>
@@ -13562,7 +13617,7 @@
         <v>Needs</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="21" t="s">
         <v>15</v>
       </c>
@@ -13595,7 +13650,7 @@
         <v>Needs</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="21" t="s">
         <v>18</v>
       </c>
@@ -13628,7 +13683,7 @@
         <v>Needs</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="21" t="s">
         <v>21</v>
       </c>
@@ -13661,7 +13716,7 @@
         <v>Needs</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="21" t="s">
         <v>24</v>
       </c>
@@ -13694,7 +13749,7 @@
         <v>Needs</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="21" t="s">
         <v>25</v>
       </c>
@@ -13727,7 +13782,7 @@
         <v>Needs</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="21" t="s">
         <v>28</v>
       </c>
@@ -13760,7 +13815,7 @@
         <v>Needs</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="21" t="s">
         <v>32</v>
       </c>
@@ -13793,7 +13848,7 @@
         <v>Wants</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="21" t="s">
         <v>34</v>
       </c>
@@ -13826,7 +13881,7 @@
         <v>Wants</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="21" t="s">
         <v>36</v>
       </c>
@@ -13859,7 +13914,7 @@
         <v>Wants</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="21" t="s">
         <v>38</v>
       </c>
@@ -13892,7 +13947,7 @@
         <v>Wants</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="21" t="s">
         <v>40</v>
       </c>
@@ -13925,7 +13980,7 @@
         <v>Wants</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="19" t="s">
         <v>66</v>
       </c>
@@ -13958,7 +14013,7 @@
         <v>Wants</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="19" t="s">
         <v>67</v>
       </c>
@@ -13979,7 +14034,7 @@
         <v>Savings</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H21" s="11" t="str">
         <f aca="false">IF(Setup!E24="","",Setup!E24)</f>
         <v>Sinking funds</v>
@@ -13993,7 +14048,7 @@
         <v>Savings</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H22" s="11" t="str">
         <f aca="false">IF(Setup!E25="","",Setup!E25)</f>
         <v>Retirement</v>
@@ -14027,7 +14082,7 @@
         <v>Debt</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="11" t="s">
         <v>69</v>
       </c>
@@ -14048,7 +14103,7 @@
         <v>Debt</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="11" t="s">
         <v>70</v>
       </c>
@@ -14069,7 +14124,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="11" t="s">
         <v>9</v>
       </c>
@@ -14090,7 +14145,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="11" t="s">
         <v>8</v>
       </c>
@@ -14111,7 +14166,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H28" s="11" t="str">
         <f aca="false">IF(Setup!E31="","",Setup!E31)</f>
         <v/>
@@ -14125,7 +14180,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H29" s="11" t="str">
         <f aca="false">IF(Setup!E32="","",Setup!E32)</f>
         <v/>
@@ -14139,7 +14194,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H30" s="11" t="str">
         <f aca="false">IF(Setup!E33="","",Setup!E33)</f>
         <v/>
@@ -14153,7 +14208,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H31" s="11" t="str">
         <f aca="false">IF(Setup!E34="","",Setup!E34)</f>
         <v/>
@@ -14167,7 +14222,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H32" s="11" t="str">
         <f aca="false">IF(Setup!E35="","",Setup!E35)</f>
         <v/>
@@ -14181,7 +14236,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H33" s="11" t="str">
         <f aca="false">IF(Setup!E36="","",Setup!E36)</f>
         <v/>
@@ -14195,7 +14250,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H34" s="11" t="str">
         <f aca="false">IF(Setup!E37="","",Setup!E37)</f>
         <v/>
@@ -14209,7 +14264,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H35" s="11" t="str">
         <f aca="false">IF(Setup!E38="","",Setup!E38)</f>
         <v/>
@@ -14223,7 +14278,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H36" s="11" t="str">
         <f aca="false">IF(Setup!E39="","",Setup!E39)</f>
         <v/>
@@ -14342,7 +14397,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="10" t="s">
         <v>74</v>
       </c>
@@ -14704,7 +14759,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -14754,7 +14809,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -14778,7 +14833,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29" t="n">
         <v>46390</v>
       </c>
@@ -14799,7 +14854,7 @@
         <v>2112.09</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29" t="n">
         <v>46391</v>
       </c>
@@ -14820,7 +14875,7 @@
         <v>1787.91</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29" t="n">
         <v>46393</v>
       </c>
@@ -14841,7 +14896,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29" t="n">
         <v>46396</v>
       </c>
@@ -14855,7 +14910,7 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29" t="n">
         <v>46398</v>
       </c>
@@ -14885,7 +14940,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29" t="n">
         <v>46401</v>
       </c>
@@ -14923,7 +14978,7 @@
         <v>█████████░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29" t="n">
         <v>46402</v>
       </c>
@@ -14961,7 +15016,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29" t="n">
         <v>46405</v>
       </c>
@@ -14999,7 +15054,7 @@
         <v>████░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29" t="n">
         <v>46408</v>
       </c>
@@ -15037,7 +15092,7 @@
         <v>███░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29" t="n">
         <v>46411</v>
       </c>
@@ -15075,7 +15130,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29" t="n">
         <v>46412</v>
       </c>
@@ -15113,7 +15168,7 @@
         <v>██████░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -15143,7 +15198,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -15173,7 +15228,7 @@
         <v>███░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -15203,7 +15258,7 @@
         <v>█████░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -15233,7 +15288,7 @@
         <v>████░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -15263,7 +15318,7 @@
         <v>██████████</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -15293,7 +15348,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -15323,7 +15378,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -15353,7 +15408,7 @@
         <v>██████████</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -15383,7 +15438,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -15413,7 +15468,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -15443,7 +15498,7 @@
         <v>██████████</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -15473,7 +15528,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -15503,7 +15558,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -15533,7 +15588,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -15563,7 +15618,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -15593,7 +15648,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -15623,7 +15678,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -15653,7 +15708,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -15683,7 +15738,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -15713,7 +15768,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -15743,7 +15798,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -15773,7 +15828,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -15803,7 +15858,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -15833,275 +15888,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -16151,7 +16211,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -16201,7 +16261,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -16225,7 +16285,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -16238,7 +16298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -16251,7 +16311,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -16264,13 +16324,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -16292,7 +16352,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -16322,7 +16382,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -16352,7 +16412,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -16382,7 +16442,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -16412,7 +16472,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -16442,7 +16502,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -16472,7 +16532,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -16502,7 +16562,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -16532,7 +16592,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -16562,7 +16622,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -16592,7 +16652,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -16622,7 +16682,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -16652,7 +16712,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -16682,7 +16742,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -16712,7 +16772,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -16742,7 +16802,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -16772,7 +16832,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -16802,7 +16862,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -16832,7 +16892,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -16862,7 +16922,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -16892,7 +16952,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -16922,7 +16982,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -16952,7 +17012,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -16982,7 +17042,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -17012,7 +17072,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -17042,7 +17102,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -17072,7 +17132,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -17102,7 +17162,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -17132,7 +17192,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -17162,7 +17222,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -17192,275 +17252,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -17510,7 +17575,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -17560,7 +17625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -17584,7 +17649,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -17597,7 +17662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -17610,7 +17675,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -17623,13 +17688,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -17651,7 +17716,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -17681,7 +17746,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -17711,7 +17776,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -17741,7 +17806,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -17771,7 +17836,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -17801,7 +17866,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -17831,7 +17896,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -17861,7 +17926,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -17891,7 +17956,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -17921,7 +17986,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -17951,7 +18016,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -17981,7 +18046,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -18011,7 +18076,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -18041,7 +18106,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -18071,7 +18136,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -18101,7 +18166,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -18131,7 +18196,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -18161,7 +18226,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -18191,7 +18256,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -18221,7 +18286,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -18251,7 +18316,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -18281,7 +18346,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -18311,7 +18376,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -18341,7 +18406,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -18371,7 +18436,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -18401,7 +18466,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -18431,7 +18496,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -18461,7 +18526,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -18491,7 +18556,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -18521,7 +18586,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -18551,275 +18616,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -18869,7 +18939,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -18919,7 +18989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -18943,7 +19013,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -18956,7 +19026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -18969,7 +19039,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -18982,13 +19052,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -19010,7 +19080,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -19040,7 +19110,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -19070,7 +19140,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -19100,7 +19170,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -19130,7 +19200,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -19160,7 +19230,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -19190,7 +19260,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -19220,7 +19290,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -19250,7 +19320,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -19280,7 +19350,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -19310,7 +19380,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -19340,7 +19410,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -19370,7 +19440,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -19400,7 +19470,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -19430,7 +19500,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -19460,7 +19530,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -19490,7 +19560,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -19520,7 +19590,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -19550,7 +19620,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -19580,7 +19650,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -19610,7 +19680,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -19640,7 +19710,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -19670,7 +19740,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -19700,7 +19770,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -19730,7 +19800,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -19760,7 +19830,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -19790,7 +19860,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -19820,7 +19890,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -19850,7 +19920,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -19880,7 +19950,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -19910,275 +19980,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -20228,7 +20303,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -20278,7 +20353,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -20302,7 +20377,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -20315,7 +20390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -20328,7 +20403,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -20341,13 +20416,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -20369,7 +20444,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -20399,7 +20474,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -20429,7 +20504,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -20459,7 +20534,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -20489,7 +20564,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -20519,7 +20594,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -20549,7 +20624,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -20579,7 +20654,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -20609,7 +20684,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -20639,7 +20714,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -20669,7 +20744,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -20699,7 +20774,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -20729,7 +20804,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -20759,7 +20834,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -20789,7 +20864,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -20819,7 +20894,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -20849,7 +20924,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -20879,7 +20954,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -20909,7 +20984,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -20939,7 +21014,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -20969,7 +21044,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -20999,7 +21074,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -21029,7 +21104,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -21059,7 +21134,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -21089,7 +21164,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -21119,7 +21194,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -21149,7 +21224,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -21179,7 +21254,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -21209,7 +21284,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -21239,7 +21314,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -21269,275 +21344,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>
@@ -21587,7 +21667,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L86"/>
+  <dimension ref="B2:L87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -21637,7 +21717,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
         <v>100</v>
       </c>
@@ -21661,7 +21741,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29"/>
       <c r="C7" s="30"/>
       <c r="D7" s="17"/>
@@ -21674,7 +21754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29"/>
       <c r="C8" s="30"/>
       <c r="D8" s="17"/>
@@ -21687,7 +21767,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29"/>
       <c r="C9" s="30"/>
       <c r="D9" s="17"/>
@@ -21700,13 +21780,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29"/>
       <c r="C10" s="30"/>
       <c r="D10" s="17"/>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29"/>
       <c r="C11" s="30"/>
       <c r="D11" s="17"/>
@@ -21728,7 +21808,7 @@
       </c>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29"/>
       <c r="C12" s="30"/>
       <c r="D12" s="17"/>
@@ -21758,7 +21838,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29"/>
       <c r="C13" s="30"/>
       <c r="D13" s="17"/>
@@ -21788,7 +21868,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29"/>
       <c r="C14" s="30"/>
       <c r="D14" s="17"/>
@@ -21818,7 +21898,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="29"/>
       <c r="C15" s="30"/>
       <c r="D15" s="17"/>
@@ -21848,7 +21928,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29"/>
       <c r="C16" s="30"/>
       <c r="D16" s="17"/>
@@ -21878,7 +21958,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29"/>
       <c r="C17" s="30"/>
       <c r="D17" s="17"/>
@@ -21908,7 +21988,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29"/>
       <c r="C18" s="30"/>
       <c r="D18" s="17"/>
@@ -21938,7 +22018,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29"/>
       <c r="C19" s="30"/>
       <c r="D19" s="17"/>
@@ -21968,7 +22048,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="29"/>
       <c r="C20" s="30"/>
       <c r="D20" s="17"/>
@@ -21998,7 +22078,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29"/>
       <c r="C21" s="30"/>
       <c r="D21" s="17"/>
@@ -22028,7 +22108,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29"/>
       <c r="C22" s="30"/>
       <c r="D22" s="17"/>
@@ -22058,7 +22138,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29"/>
       <c r="C23" s="30"/>
       <c r="D23" s="17"/>
@@ -22088,7 +22168,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="29"/>
       <c r="C24" s="30"/>
       <c r="D24" s="17"/>
@@ -22118,7 +22198,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29"/>
       <c r="C25" s="30"/>
       <c r="D25" s="17"/>
@@ -22148,7 +22228,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29"/>
       <c r="C26" s="30"/>
       <c r="D26" s="17"/>
@@ -22178,7 +22258,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29"/>
       <c r="C27" s="30"/>
       <c r="D27" s="17"/>
@@ -22208,7 +22288,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29"/>
       <c r="C28" s="30"/>
       <c r="D28" s="17"/>
@@ -22238,7 +22318,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29"/>
       <c r="C29" s="30"/>
       <c r="D29" s="17"/>
@@ -22268,7 +22348,7 @@
         <v>░░░░░░░░░░</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="29"/>
       <c r="C30" s="30"/>
       <c r="D30" s="17"/>
@@ -22298,7 +22378,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29"/>
       <c r="C31" s="30"/>
       <c r="D31" s="17"/>
@@ -22328,7 +22408,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29"/>
       <c r="C32" s="30"/>
       <c r="D32" s="17"/>
@@ -22358,7 +22438,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29"/>
       <c r="C33" s="30"/>
       <c r="D33" s="17"/>
@@ -22388,7 +22468,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29"/>
       <c r="C34" s="30"/>
       <c r="D34" s="17"/>
@@ -22418,7 +22498,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="17"/>
@@ -22448,7 +22528,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="29"/>
       <c r="C36" s="30"/>
       <c r="D36" s="17"/>
@@ -22478,7 +22558,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="29"/>
       <c r="C37" s="30"/>
       <c r="D37" s="17"/>
@@ -22508,7 +22588,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="29"/>
       <c r="C38" s="30"/>
       <c r="D38" s="17"/>
@@ -22538,7 +22618,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="29"/>
       <c r="C39" s="30"/>
       <c r="D39" s="17"/>
@@ -22568,7 +22648,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="29"/>
       <c r="C40" s="30"/>
       <c r="D40" s="17"/>
@@ -22598,7 +22678,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="29"/>
       <c r="C41" s="30"/>
       <c r="D41" s="17"/>
@@ -22628,275 +22708,280 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="29"/>
       <c r="C42" s="30"/>
       <c r="D42" s="17"/>
       <c r="E42" s="26"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="29"/>
       <c r="C43" s="30"/>
       <c r="D43" s="17"/>
       <c r="E43" s="26"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="29"/>
       <c r="C44" s="30"/>
       <c r="D44" s="17"/>
       <c r="E44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="29"/>
       <c r="C45" s="30"/>
       <c r="D45" s="17"/>
       <c r="E45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="29"/>
       <c r="C46" s="30"/>
       <c r="D46" s="17"/>
       <c r="E46" s="26"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="29"/>
       <c r="C47" s="30"/>
       <c r="D47" s="17"/>
       <c r="E47" s="26"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="29"/>
       <c r="C48" s="30"/>
       <c r="D48" s="17"/>
       <c r="E48" s="26"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="29"/>
       <c r="C49" s="30"/>
       <c r="D49" s="17"/>
       <c r="E49" s="26"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="29"/>
       <c r="C50" s="30"/>
       <c r="D50" s="17"/>
       <c r="E50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="29"/>
       <c r="C51" s="30"/>
       <c r="D51" s="17"/>
       <c r="E51" s="26"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="29"/>
       <c r="C52" s="30"/>
       <c r="D52" s="17"/>
       <c r="E52" s="26"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="29"/>
       <c r="C53" s="30"/>
       <c r="D53" s="17"/>
       <c r="E53" s="26"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="29"/>
       <c r="C54" s="30"/>
       <c r="D54" s="17"/>
       <c r="E54" s="26"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29"/>
       <c r="C55" s="30"/>
       <c r="D55" s="17"/>
       <c r="E55" s="26"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="29"/>
       <c r="C56" s="30"/>
       <c r="D56" s="17"/>
       <c r="E56" s="26"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="29"/>
       <c r="C57" s="30"/>
       <c r="D57" s="17"/>
       <c r="E57" s="26"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="29"/>
       <c r="C58" s="30"/>
       <c r="D58" s="17"/>
       <c r="E58" s="26"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="29"/>
       <c r="C59" s="30"/>
       <c r="D59" s="17"/>
       <c r="E59" s="26"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="29"/>
       <c r="C60" s="30"/>
       <c r="D60" s="17"/>
       <c r="E60" s="26"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="29"/>
       <c r="C61" s="30"/>
       <c r="D61" s="17"/>
       <c r="E61" s="26"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="29"/>
       <c r="C62" s="30"/>
       <c r="D62" s="17"/>
       <c r="E62" s="26"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="17"/>
       <c r="E63" s="26"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
       <c r="D64" s="17"/>
       <c r="E64" s="26"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="29"/>
       <c r="C65" s="30"/>
       <c r="D65" s="17"/>
       <c r="E65" s="26"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="29"/>
       <c r="C66" s="30"/>
       <c r="D66" s="17"/>
       <c r="E66" s="26"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="29"/>
       <c r="C67" s="30"/>
       <c r="D67" s="17"/>
       <c r="E67" s="26"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B68" s="29"/>
       <c r="C68" s="30"/>
       <c r="D68" s="17"/>
       <c r="E68" s="26"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="29"/>
       <c r="C69" s="30"/>
       <c r="D69" s="17"/>
       <c r="E69" s="26"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="29"/>
       <c r="C70" s="30"/>
       <c r="D70" s="17"/>
       <c r="E70" s="26"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B71" s="29"/>
       <c r="C71" s="30"/>
       <c r="D71" s="17"/>
       <c r="E71" s="26"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="29"/>
       <c r="C72" s="30"/>
       <c r="D72" s="17"/>
       <c r="E72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="29"/>
       <c r="C73" s="30"/>
       <c r="D73" s="17"/>
       <c r="E73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="29"/>
       <c r="C74" s="30"/>
       <c r="D74" s="17"/>
       <c r="E74" s="26"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="29"/>
       <c r="C75" s="30"/>
       <c r="D75" s="17"/>
       <c r="E75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29"/>
       <c r="C76" s="30"/>
       <c r="D76" s="17"/>
       <c r="E76" s="26"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="29"/>
       <c r="C77" s="30"/>
       <c r="D77" s="17"/>
       <c r="E77" s="26"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="29"/>
       <c r="C78" s="30"/>
       <c r="D78" s="17"/>
       <c r="E78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="29"/>
       <c r="C79" s="30"/>
       <c r="D79" s="17"/>
       <c r="E79" s="26"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="29"/>
       <c r="C80" s="30"/>
       <c r="D80" s="17"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="29"/>
       <c r="C81" s="30"/>
       <c r="D81" s="17"/>
       <c r="E81" s="26"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="29"/>
       <c r="C82" s="30"/>
       <c r="D82" s="17"/>
       <c r="E82" s="26"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="29"/>
       <c r="C83" s="30"/>
       <c r="D83" s="17"/>
       <c r="E83" s="26"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="29"/>
       <c r="C84" s="30"/>
       <c r="D84" s="17"/>
       <c r="E84" s="26"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="29"/>
       <c r="C85" s="30"/>
       <c r="D85" s="17"/>
       <c r="E85" s="26"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="29"/>
       <c r="C86" s="30"/>
       <c r="D86" s="17"/>
       <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="28" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatColumns="false" formatRows="false" insertRows="false" sort="false" autoFilter="false"/>

--- a/data/products/p-gsb-001/work/Clear-Budget.xlsx
+++ b/data/products/p-gsb-001/work/Clear-Budget.xlsx
@@ -533,7 +533,7 @@
     <t xml:space="preserve">Interest saved</t>
   </si>
   <si>
-    <t xml:space="preserve">Medical bill</t>
+    <t xml:space="preserve">Store card</t>
   </si>
   <si>
     <t xml:space="preserve">Car loan</t>
@@ -1347,11 +1347,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="31805084"/>
-        <c:axId val="59715233"/>
+        <c:axId val="26444737"/>
+        <c:axId val="45113722"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="31805084"/>
+        <c:axId val="26444737"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1383,7 +1383,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59715233"/>
+        <c:crossAx val="45113722"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1391,7 +1391,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="59715233"/>
+        <c:axId val="45113722"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1433,7 +1433,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31805084"/>
+        <c:crossAx val="26444737"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1853,7 +1853,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>858240</xdr:colOff>
+      <xdr:colOff>505800</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>42120</xdr:rowOff>
     </xdr:to>
@@ -10920,7 +10920,7 @@
       <c r="D7" s="26" t="n">
         <v>1400</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="34" t="s">
         <v>134</v>
       </c>
       <c r="F7" s="34"/>
@@ -10946,7 +10946,7 @@
       <c r="D8" s="26" t="n">
         <v>95</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="34" t="s">
         <v>134</v>
       </c>
       <c r="F8" s="34"/>
@@ -10972,7 +10972,7 @@
       <c r="D9" s="26" t="n">
         <v>15.99</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="34" t="s">
         <v>134</v>
       </c>
       <c r="F9" s="34"/>
@@ -10998,7 +10998,7 @@
       <c r="D10" s="26" t="n">
         <v>160</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="34" t="s">
         <v>136</v>
       </c>
       <c r="F10" s="34"/>
@@ -11024,7 +11024,7 @@
       <c r="D11" s="26" t="n">
         <v>90</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="34" t="s">
         <v>136</v>
       </c>
       <c r="F11" s="34"/>
@@ -11050,7 +11050,7 @@
       <c r="D12" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="34" t="s">
         <v>136</v>
       </c>
       <c r="F12" s="34"/>
@@ -11070,7 +11070,7 @@
       <c r="B13" s="17"/>
       <c r="C13" s="25"/>
       <c r="D13" s="26"/>
-      <c r="E13" s="17"/>
+      <c r="E13" s="34"/>
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="34"/>
@@ -11088,7 +11088,7 @@
       <c r="B14" s="17"/>
       <c r="C14" s="25"/>
       <c r="D14" s="26"/>
-      <c r="E14" s="17"/>
+      <c r="E14" s="34"/>
       <c r="F14" s="34"/>
       <c r="G14" s="34"/>
       <c r="H14" s="34"/>
@@ -11106,7 +11106,7 @@
       <c r="B15" s="17"/>
       <c r="C15" s="25"/>
       <c r="D15" s="26"/>
-      <c r="E15" s="17"/>
+      <c r="E15" s="34"/>
       <c r="F15" s="34"/>
       <c r="G15" s="34"/>
       <c r="H15" s="34"/>
@@ -11124,7 +11124,7 @@
       <c r="B16" s="17"/>
       <c r="C16" s="25"/>
       <c r="D16" s="26"/>
-      <c r="E16" s="17"/>
+      <c r="E16" s="34"/>
       <c r="F16" s="34"/>
       <c r="G16" s="34"/>
       <c r="H16" s="34"/>
@@ -11142,7 +11142,7 @@
       <c r="B17" s="17"/>
       <c r="C17" s="25"/>
       <c r="D17" s="26"/>
-      <c r="E17" s="17"/>
+      <c r="E17" s="34"/>
       <c r="F17" s="34"/>
       <c r="G17" s="34"/>
       <c r="H17" s="34"/>
@@ -11160,7 +11160,7 @@
       <c r="B18" s="17"/>
       <c r="C18" s="25"/>
       <c r="D18" s="26"/>
-      <c r="E18" s="17"/>
+      <c r="E18" s="34"/>
       <c r="F18" s="34"/>
       <c r="G18" s="34"/>
       <c r="H18" s="34"/>
@@ -11178,7 +11178,7 @@
       <c r="B19" s="17"/>
       <c r="C19" s="25"/>
       <c r="D19" s="26"/>
-      <c r="E19" s="17"/>
+      <c r="E19" s="34"/>
       <c r="F19" s="34"/>
       <c r="G19" s="34"/>
       <c r="H19" s="34"/>
@@ -11196,7 +11196,7 @@
       <c r="B20" s="17"/>
       <c r="C20" s="25"/>
       <c r="D20" s="26"/>
-      <c r="E20" s="17"/>
+      <c r="E20" s="34"/>
       <c r="F20" s="34"/>
       <c r="G20" s="34"/>
       <c r="H20" s="34"/>
@@ -11214,7 +11214,7 @@
       <c r="B21" s="17"/>
       <c r="C21" s="25"/>
       <c r="D21" s="26"/>
-      <c r="E21" s="17"/>
+      <c r="E21" s="34"/>
       <c r="F21" s="34"/>
       <c r="G21" s="34"/>
       <c r="H21" s="34"/>
@@ -11232,7 +11232,7 @@
       <c r="B22" s="17"/>
       <c r="C22" s="25"/>
       <c r="D22" s="26"/>
-      <c r="E22" s="17"/>
+      <c r="E22" s="34"/>
       <c r="F22" s="34"/>
       <c r="G22" s="34"/>
       <c r="H22" s="34"/>
@@ -11250,7 +11250,7 @@
       <c r="B23" s="17"/>
       <c r="C23" s="25"/>
       <c r="D23" s="26"/>
-      <c r="E23" s="17"/>
+      <c r="E23" s="34"/>
       <c r="F23" s="34"/>
       <c r="G23" s="34"/>
       <c r="H23" s="34"/>
@@ -11268,7 +11268,7 @@
       <c r="B24" s="17"/>
       <c r="C24" s="25"/>
       <c r="D24" s="26"/>
-      <c r="E24" s="17"/>
+      <c r="E24" s="34"/>
       <c r="F24" s="34"/>
       <c r="G24" s="34"/>
       <c r="H24" s="34"/>
@@ -11286,7 +11286,7 @@
       <c r="B25" s="17"/>
       <c r="C25" s="25"/>
       <c r="D25" s="26"/>
-      <c r="E25" s="17"/>
+      <c r="E25" s="34"/>
       <c r="F25" s="34"/>
       <c r="G25" s="34"/>
       <c r="H25" s="34"/>
@@ -11304,7 +11304,7 @@
       <c r="B26" s="17"/>
       <c r="C26" s="25"/>
       <c r="D26" s="26"/>
-      <c r="E26" s="17"/>
+      <c r="E26" s="34"/>
       <c r="F26" s="34"/>
       <c r="G26" s="34"/>
       <c r="H26" s="34"/>
@@ -11322,7 +11322,7 @@
       <c r="B27" s="17"/>
       <c r="C27" s="25"/>
       <c r="D27" s="26"/>
-      <c r="E27" s="17"/>
+      <c r="E27" s="34"/>
       <c r="F27" s="34"/>
       <c r="G27" s="34"/>
       <c r="H27" s="34"/>
@@ -11340,7 +11340,7 @@
       <c r="B28" s="17"/>
       <c r="C28" s="25"/>
       <c r="D28" s="26"/>
-      <c r="E28" s="17"/>
+      <c r="E28" s="34"/>
       <c r="F28" s="34"/>
       <c r="G28" s="34"/>
       <c r="H28" s="34"/>
@@ -11358,7 +11358,7 @@
       <c r="B29" s="17"/>
       <c r="C29" s="25"/>
       <c r="D29" s="26"/>
-      <c r="E29" s="17"/>
+      <c r="E29" s="34"/>
       <c r="F29" s="34"/>
       <c r="G29" s="34"/>
       <c r="H29" s="34"/>
@@ -11376,7 +11376,7 @@
       <c r="B30" s="17"/>
       <c r="C30" s="25"/>
       <c r="D30" s="26"/>
-      <c r="E30" s="17"/>
+      <c r="E30" s="34"/>
       <c r="F30" s="34"/>
       <c r="G30" s="34"/>
       <c r="H30" s="34"/>
@@ -11394,7 +11394,7 @@
       <c r="B31" s="17"/>
       <c r="C31" s="25"/>
       <c r="D31" s="26"/>
-      <c r="E31" s="17"/>
+      <c r="E31" s="34"/>
       <c r="F31" s="34"/>
       <c r="G31" s="34"/>
       <c r="H31" s="34"/>
@@ -12879,10 +12879,10 @@
         <v>600</v>
       </c>
       <c r="D10" s="38" t="n">
-        <v>0</v>
+        <v>0.1999</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F10" s="39" t="n">
         <f aca="false">IF(C10="","",IF($C$6="Snowball",COUNTIFS($C$10:$C$19,"&lt;"&amp;C10,$C$10:$C$19,"&lt;&gt;")+1,COUNTIFS($D$10:$D$19,"&gt;"&amp;D10,$C$10:$C$19,"&lt;&gt;")+1))</f>
@@ -12890,19 +12890,19 @@
       </c>
       <c r="G10" s="39" t="n">
         <f aca="false">IF(OR(C10="",E10=""),"",IFERROR(ROUNDUP(NPER(D10/12,-E10,C10),0),"never: raise the minimum"))</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H10" s="22" t="n">
         <f aca="false">IF(OR(C10="",E10="",NOT(ISNUMBER(G10))),"",G10*E10-C10)</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I10" s="39" t="n">
         <f aca="false">IF(OR(C10="",E10="",F10&lt;&gt;1),"",IFERROR(ROUNDUP(NPER(D10/12,-(E10+$C$7),C10),0),""))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10" s="22" t="n">
         <f aca="false">IF(OR(I10="",NOT(ISNUMBER(H10))),"",MAX(0,H10-(I10*(E10+$C$7)-C10)))</f>
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12913,7 +12913,7 @@
         <v>2400</v>
       </c>
       <c r="D11" s="38" t="n">
-        <v>0.2299</v>
+        <v>0.2499</v>
       </c>
       <c r="E11" s="26" t="n">
         <v>75</v>
@@ -12924,11 +12924,11 @@
       </c>
       <c r="G11" s="39" t="n">
         <f aca="false">IF(OR(C11="",E11=""),"",IFERROR(ROUNDUP(NPER(D11/12,-E11,C11),0),"never: raise the minimum"))</f>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H11" s="22" t="n">
         <f aca="false">IF(OR(C11="",E11="",NOT(ISNUMBER(G11))),"",G11*E11-C11)</f>
-        <v>1425</v>
+        <v>1650</v>
       </c>
       <c r="I11" s="39" t="str">
         <f aca="false">IF(OR(C11="",E11="",F11&lt;&gt;1),"",IFERROR(ROUNDUP(NPER(D11/12,-(E11+$C$7),C11),0),""))</f>
@@ -13173,7 +13173,7 @@
       </c>
       <c r="E20" s="23" t="n">
         <f aca="false">SUM(E10:E19)</f>
-        <v>515</v>
+        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -13517,7 +13517,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
